--- a/artfynd/A 40420-2023 artfynd.xlsx
+++ b/artfynd/A 40420-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40420-2023 artfynd.xlsx
+++ b/artfynd/A 40420-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112518040</v>
+        <v>112517256</v>
       </c>
       <c r="B2" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584177</v>
+        <v>584275</v>
       </c>
       <c r="R2" t="n">
-        <v>7054935</v>
+        <v>7054599</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,56 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112517931</v>
+        <v>112517227</v>
       </c>
       <c r="B3" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584130</v>
+        <v>584295</v>
       </c>
       <c r="R3" t="n">
-        <v>7054818</v>
+        <v>7054594</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112517946</v>
+        <v>112517585</v>
       </c>
       <c r="B4" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,35 +902,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584129</v>
+        <v>584202</v>
       </c>
       <c r="R4" t="n">
-        <v>7054821</v>
+        <v>7054691</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,51 +999,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112517383</v>
+        <v>112517573</v>
       </c>
       <c r="B5" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584277</v>
+        <v>584207</v>
       </c>
       <c r="R5" t="n">
-        <v>7054625</v>
+        <v>7054701</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,51 +1107,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112517573</v>
+        <v>112517372</v>
       </c>
       <c r="B6" t="n">
-        <v>90101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584207</v>
+        <v>584280</v>
       </c>
       <c r="R6" t="n">
-        <v>7054701</v>
+        <v>7054606</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,63 +1203,58 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112517807</v>
+        <v>112517946</v>
       </c>
       <c r="B7" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584166</v>
+        <v>584129</v>
       </c>
       <c r="R7" t="n">
-        <v>7054746</v>
+        <v>7054821</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1321,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,15 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112517585</v>
+        <v>112518033</v>
       </c>
       <c r="B8" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,35 +1334,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584202</v>
+        <v>584160</v>
       </c>
       <c r="R8" t="n">
-        <v>7054691</v>
+        <v>7054960</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,15 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112517372</v>
+        <v>112518040</v>
       </c>
       <c r="B9" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,14 +1463,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584280</v>
+        <v>584177</v>
       </c>
       <c r="R9" t="n">
-        <v>7054606</v>
+        <v>7054935</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,63 +1527,63 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112517686</v>
+        <v>112517931</v>
       </c>
       <c r="B10" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584225</v>
+        <v>584130</v>
       </c>
       <c r="R10" t="n">
-        <v>7054718</v>
+        <v>7054818</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,27 +1640,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112517993</v>
+        <v>112517318</v>
       </c>
       <c r="B11" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,18 +1680,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584128</v>
+        <v>584267</v>
       </c>
       <c r="R11" t="n">
-        <v>7054856</v>
+        <v>7054616</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,27 +1752,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112517318</v>
+        <v>112517383</v>
       </c>
       <c r="B12" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,22 +1792,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584267</v>
+        <v>584277</v>
       </c>
       <c r="R12" t="n">
-        <v>7054616</v>
+        <v>7054625</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1930,12 +1875,7 @@
         <v>112517683</v>
       </c>
       <c r="B13" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,7 +1904,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2040,51 +1980,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112517256</v>
+        <v>112517686</v>
       </c>
       <c r="B14" t="n">
-        <v>89942</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584275</v>
+        <v>584224</v>
       </c>
       <c r="R14" t="n">
-        <v>7054599</v>
+        <v>7054718</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2116,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,63 +2076,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112517227</v>
+        <v>112517775</v>
       </c>
       <c r="B15" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584294</v>
+        <v>584171</v>
       </c>
       <c r="R15" t="n">
-        <v>7054593</v>
+        <v>7054749</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2229,7 +2163,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2173,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,15 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112517775</v>
+        <v>112517807</v>
       </c>
       <c r="B16" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,22 +2228,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken (Orrmyrbäcken), Ång</t>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584171</v>
+        <v>584167</v>
       </c>
       <c r="R16" t="n">
-        <v>7054748</v>
+        <v>7054747</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2346,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,6 +2305,114 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112517993</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Orrmyrbäcken, Orrmyrbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584128</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7054856</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40420-2023 artfynd.xlsx
+++ b/artfynd/A 40420-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517227</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517585</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517573</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517372</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517946</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112518033</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112518040</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517931</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517318</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517383</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517683</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2085,6 +2150,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517686</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517775</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,6 +2380,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517807</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2413,8 +2493,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112517993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>